--- a/public/templates/farmtrack-import-template.xlsx
+++ b/public/templates/farmtrack-import-template.xlsx
@@ -1,48 +1,192 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Camps" sheetId="1" r:id="rId1"/>
-    <sheet name="Animals" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Camps" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Animals" state="visible" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="54">
+  <si>
+    <t>camp_name</t>
+  </si>
+  <si>
+    <t>size_hectares</t>
+  </si>
+  <si>
+    <t>water_source</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>Rivier</t>
+  </si>
+  <si>
+    <t>River</t>
+  </si>
+  <si>
+    <t>Best grazing on the farm</t>
+  </si>
+  <si>
+    <t>Koppie</t>
+  </si>
+  <si>
+    <t>Borehole</t>
+  </si>
+  <si>
+    <t>Rocky terrain — use for dry cows</t>
+  </si>
+  <si>
+    <t>Kraal</t>
+  </si>
+  <si>
+    <t>Trough</t>
+  </si>
+  <si>
+    <t>Treatment camp near house</t>
+  </si>
+  <si>
+    <t>animal_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>date_of_birth</t>
+  </si>
+  <si>
+    <t>breed</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>current_camp</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>mother_id</t>
+  </si>
+  <si>
+    <t>father_id</t>
+  </si>
+  <si>
+    <t>date_added</t>
+  </si>
+  <si>
+    <t>B-001</t>
+  </si>
+  <si>
+    <t>Atlas</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>2021-03-15</t>
+  </si>
+  <si>
+    <t>Bonsmara</t>
+  </si>
+  <si>
+    <t>Bull</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Stud bull</t>
+  </si>
+  <si>
+    <t>2024-01-10</t>
+  </si>
+  <si>
+    <t>C-001</t>
+  </si>
+  <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>2020-08-22</t>
+  </si>
+  <si>
+    <t>Cow</t>
+  </si>
+  <si>
+    <t>C-050</t>
+  </si>
+  <si>
+    <t>Pregnant</t>
+  </si>
+  <si>
+    <t>H-001</t>
+  </si>
+  <si>
+    <t>2023-06-10</t>
+  </si>
+  <si>
+    <t>Heifer</t>
+  </si>
+  <si>
+    <t>2024-06-10</t>
+  </si>
+  <si>
+    <t>K-001</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>Calf</t>
+  </si>
+  <si>
+    <t>Born on farm</t>
+  </si>
+  <si>
+    <t>O-001</t>
+  </si>
+  <si>
+    <t>2021-11-03</t>
+  </si>
+  <si>
+    <t>Ox</t>
+  </si>
+  <si>
+    <t>Castrated 2022</t>
+  </si>
+  <si>
+    <t>2024-03-01</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,13 +210,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,327 +549,322 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="35.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>camp_name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>size_hectares</v>
-      </c>
-      <c r="C1" t="str">
-        <v>water_source</v>
-      </c>
-      <c r="D1" t="str">
-        <v>notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Rivier</v>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
       </c>
       <c r="B2">
         <v>150</v>
       </c>
-      <c r="C2" t="str">
-        <v>River</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Best grazing on the farm</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Koppie</v>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
       </c>
       <c r="B3">
         <v>80</v>
       </c>
-      <c r="C3" t="str">
-        <v>Borehole</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Rocky terrain — use for dry cows</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Kraal</v>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
       </c>
       <c r="B4">
         <v>15</v>
       </c>
-      <c r="C4" t="str">
-        <v>Trough</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Treatment camp near house</v>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="20.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>animal_id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>sex</v>
-      </c>
-      <c r="D1" t="str">
-        <v>date_of_birth</v>
-      </c>
-      <c r="E1" t="str">
-        <v>breed</v>
-      </c>
-      <c r="F1" t="str">
-        <v>category</v>
-      </c>
-      <c r="G1" t="str">
-        <v>current_camp</v>
-      </c>
-      <c r="H1" t="str">
-        <v>status</v>
-      </c>
-      <c r="I1" t="str">
-        <v>mother_id</v>
-      </c>
-      <c r="J1" t="str">
-        <v>father_id</v>
-      </c>
-      <c r="K1" t="str">
-        <v>notes</v>
-      </c>
-      <c r="L1" t="str">
-        <v>date_added</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>B-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Atlas</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Male</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2021-03-15</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Bonsmara</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Bull</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Kraal</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Active</v>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v>Stud bull</v>
-      </c>
-      <c r="L2" t="str">
-        <v>2024-01-10</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>C-001</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Bella</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Female</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2020-08-22</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Bonsmara</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Cow</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Rivier</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Active</v>
-      </c>
-      <c r="I3" t="str">
-        <v>C-050</v>
-      </c>
-      <c r="J3" t="str">
-        <v>B-001</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Pregnant</v>
-      </c>
-      <c r="L3" t="str">
-        <v>2024-01-10</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>H-001</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v>Female</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2023-06-10</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Bonsmara</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Heifer</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Koppie</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Active</v>
-      </c>
-      <c r="I4" t="str">
-        <v>C-001</v>
-      </c>
-      <c r="J4" t="str">
-        <v>B-001</v>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>2024-06-10</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>K-001</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v>Male</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2025-09-15</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Bonsmara</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Calf</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Rivier</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Active</v>
-      </c>
-      <c r="I5" t="str">
-        <v>C-001</v>
-      </c>
-      <c r="J5" t="str">
-        <v>B-001</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Born on farm</v>
-      </c>
-      <c r="L5" t="str">
-        <v>2025-09-15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>O-001</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v>Male</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2021-11-03</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Bonsmara</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Ox</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Koppie</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Active</v>
-      </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v>Castrated 2022</v>
-      </c>
-      <c r="L6" t="str">
-        <v>2024-03-01</v>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>